--- a/data/satisfaction_detail/2026/1-8月/展览主承办.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/展览主承办.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.51</v>
+        <v>9.618697543636268</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.69</v>
+        <v>9.757013104143457</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.91</v>
+        <v>9.809952252108866</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.94</v>
+        <v>9.82702636744655</v>
       </c>
     </row>
     <row r="4">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.91</v>
+        <v>9.901286540400021</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>10</v>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.88461934320123</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>10</v>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.965276672502519</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>10</v>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.98</v>
+        <v>9.983332802801209</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>10</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>9.93</v>
+        <v>9.788540506127646</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.522994323306277</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.795321767733036</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.795321767733036</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.789766035333439</v>
       </c>
     </row>
     <row r="11">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>9.91</v>
+        <v>9.748098042336464</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.93</v>
+        <v>9.782903071780996</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.58</v>
+        <v>9.558777123454826</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.720000000000001</v>
+        <v>9.637537800413815</v>
       </c>
     </row>
     <row r="13">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.92</v>
+        <v>9.730041912037773</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.84</v>
+        <v>9.696952623481353</v>
       </c>
     </row>
     <row r="14">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.9</v>
+        <v>9.771873308928855</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.98</v>
+        <v>9.810600031831928</v>
       </c>
     </row>
     <row r="15">
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.98</v>
+        <v>9.810600031831928</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>9.93</v>
+        <v>9.759209507135656</v>
       </c>
     </row>
     <row r="16">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>9.84</v>
+        <v>9.667440713035175</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9.98</v>
+        <v>9.810600031831928</v>
       </c>
     </row>
     <row r="17">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>9.98</v>
+        <v>9.810600031831928</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.793932834633138</v>
       </c>
     </row>
     <row r="18">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>9.93</v>
+        <v>9.766154172635153</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>10</v>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>9.529999999999999</v>
+        <v>9.592559286964827</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>9.93</v>
+        <v>9.823659610589422</v>
       </c>
     </row>
     <row r="20">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>9.67</v>
+        <v>9.727833306806728</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.721708313438379</v>
       </c>
     </row>
     <row r="21">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>9.5</v>
+        <v>9.610083293543425</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.789766035333439</v>
       </c>
     </row>
     <row r="22">
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>9.56</v>
+        <v>9.479036023131201</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.789766035333439</v>
       </c>
     </row>
     <row r="23">
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>9.720000000000001</v>
+        <v>9.578712398535732</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.789766035333439</v>
       </c>
     </row>
     <row r="24">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>9.390000000000001</v>
+        <v>9.557630643535466</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.95138734150353</v>
       </c>
     </row>
     <row r="25">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>9.43</v>
+        <v>9.582975754681947</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>9.93</v>
+        <v>9.771791606981804</v>
       </c>
     </row>
     <row r="26">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>9.43</v>
+        <v>9.613433073372594</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>9.91</v>
+        <v>9.946076714945089</v>
       </c>
     </row>
     <row r="27">
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>9.75</v>
+        <v>9.630225476152582</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>9.869999999999999</v>
+        <v>9.724486179638177</v>
       </c>
     </row>
     <row r="28">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>9.19</v>
+        <v>9.282858171346293</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.801843052555796</v>
       </c>
     </row>
     <row r="29">
@@ -826,7 +826,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>9.9</v>
+        <v>9.933384223918575</v>
       </c>
     </row>
     <row r="30">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>9.93</v>
+        <v>9.767443896227917</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>9.91</v>
+        <v>9.769013740782004</v>
       </c>
     </row>
     <row r="31">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.766480980423365</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.728734680884926</v>
       </c>
     </row>
     <row r="32">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>8.83</v>
+        <v>9.098023064250413</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>9</v>
+        <v>9.308072487644152</v>
       </c>
     </row>
     <row r="33">
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>9.33</v>
+        <v>9.308072487644152</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>9.67</v>
+        <v>9.728171334431632</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>9</v>
+        <v>8.887973640856673</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>9.33</v>
+        <v>9.308072487644152</v>
       </c>
     </row>
     <row r="36">
